--- a/outputs/plan/дозаказ_под_пик_окт_дек_2026.xlsx
+++ b/outputs/plan/дозаказ_под_пик_окт_дек_2026.xlsx
@@ -115,7 +115,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -510,14 +510,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>СПИСОК НА ДОЗАКАЗ ПОД ДЕКАБРЬСКИЙ ПИК (дефицит сезона окт-дек)</t>
+          <t>СПИСОК НА ДОЗАКАЗ ПОД ДЕКАБРЬСКИЙ ПИК (обновлён: с Celimax и новинками 2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Только товары, где спрос сезона (факт окт+ноя+дек 2025) больше текущего остатка. ДОЗАКАЗ = спрос − остаток. Сумма закупа = дозаказ × себес.</t>
+          <t>Спрос сезона: сезон-2025, для новинок — факт апр-июн 2026 ×3. ДОЗАКАЗ = спрос − остаток.</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>▶ MANYO (1 поз)</t>
+          <t>▶ LANEIGE (1 поз)</t>
         </is>
       </c>
       <c r="B38" s="5" t="n"/>
@@ -1453,38 +1453,38 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+          <t>LANEIGE LIP SLEEPING MASK-BERRY [3g]</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>198156698</v>
+        <v>868761530</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>853</v>
+        <v>131</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>223</v>
+        <v>423</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>61416</v>
+        <v>25779</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>606</v>
+        <v>139</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>43632</v>
+        <v>27383</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Итого MANYO</t>
+          <t xml:space="preserve">  Итого LANEIGE</t>
         </is>
       </c>
       <c r="B40" s="9" t="n"/>
@@ -1492,20 +1492,20 @@
       <c r="D40" s="9" t="n"/>
       <c r="E40" s="9" t="n"/>
       <c r="F40" s="10" t="n">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>61416</v>
+        <v>25779</v>
       </c>
       <c r="H40" s="9" t="n"/>
       <c r="I40" s="10" t="n">
-        <v>43632</v>
+        <v>27383</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>▶ PETITFEE/PETITFEE-EYEPATCH (2 поз)</t>
+          <t>▶ MANYO (1 поз)</t>
         </is>
       </c>
       <c r="B41" s="5" t="n"/>
@@ -1520,234 +1520,234 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>198156698</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>853</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>151</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>223</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>61416</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>606</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>43632</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Итого MANYO</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>61416</v>
+      </c>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="10" t="n">
+        <v>43632</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>▶ PETITFEE/PETITFEE-EYEPATCH (2 поз)</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
           <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
         </is>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B45" s="6" t="n">
         <v>179611207</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C45" s="7" t="n">
         <v>415</v>
       </c>
-      <c r="D42" s="7" t="n">
+      <c r="D45" s="7" t="n">
         <v>608</v>
       </c>
-      <c r="E42" s="7" t="n">
+      <c r="E45" s="7" t="n">
         <v>909</v>
       </c>
-      <c r="F42" s="7" t="n">
+      <c r="F45" s="7" t="n">
         <v>301</v>
       </c>
-      <c r="G42" s="7" t="n">
+      <c r="G45" s="7" t="n">
         <v>125053</v>
       </c>
-      <c r="H42" s="7" t="n">
+      <c r="H45" s="7" t="n">
         <v>125</v>
       </c>
-      <c r="I42" s="7" t="n">
+      <c r="I45" s="7" t="n">
         <v>37625</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n">
-        <v>151175880</v>
-      </c>
-      <c r="C43" s="7" t="n">
-        <v>388</v>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>549</v>
-      </c>
-      <c r="E43" s="7" t="n">
-        <v>737</v>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>188</v>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>72882</v>
-      </c>
-      <c r="H43" s="7" t="n">
-        <v>116</v>
-      </c>
-      <c r="I43" s="7" t="n">
-        <v>21808</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Итого PETITFEE/PETITFEE-EYEPATCH</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="n"/>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="10" t="n">
-        <v>489</v>
-      </c>
-      <c r="G44" s="10" t="n">
-        <v>197935</v>
-      </c>
-      <c r="H44" s="9" t="n"/>
-      <c r="I44" s="10" t="n">
-        <v>59433</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>▶ ROUND LAB (2 поз)</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>151175880</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>388</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>549</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>737</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>188</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>72882</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>116</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>21808</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Итого PETITFEE/PETITFEE-EYEPATCH</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="10" t="n">
+        <v>489</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>197935</v>
+      </c>
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="10" t="n">
+        <v>59433</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>▶ ROUND LAB (2 поз)</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
           <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
         </is>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B49" s="6" t="n">
         <v>437190353</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C49" s="7" t="n">
         <v>1093</v>
       </c>
-      <c r="D46" s="7" t="n">
+      <c r="D49" s="7" t="n">
         <v>102</v>
       </c>
-      <c r="E46" s="7" t="n">
+      <c r="E49" s="7" t="n">
         <v>514</v>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="F49" s="7" t="n">
         <v>412</v>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="G49" s="7" t="n">
         <v>450300</v>
       </c>
-      <c r="H46" s="7" t="n">
+      <c r="H49" s="7" t="n">
         <v>328</v>
       </c>
-      <c r="I46" s="7" t="n">
+      <c r="I49" s="7" t="n">
         <v>135136</v>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n">
-        <v>437776835</v>
-      </c>
-      <c r="C47" s="7" t="n">
-        <v>820</v>
-      </c>
-      <c r="D47" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E47" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="F47" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="G47" s="7" t="n">
-        <v>54102</v>
-      </c>
-      <c r="H47" s="7" t="n">
-        <v>246</v>
-      </c>
-      <c r="I47" s="7" t="n">
-        <v>16236</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Итого ROUND LAB</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="n"/>
-      <c r="C48" s="9" t="n"/>
-      <c r="D48" s="9" t="n"/>
-      <c r="E48" s="9" t="n"/>
-      <c r="F48" s="10" t="n">
-        <v>478</v>
-      </c>
-      <c r="G48" s="10" t="n">
-        <v>504401</v>
-      </c>
-      <c r="H48" s="9" t="n"/>
-      <c r="I48" s="10" t="n">
-        <v>151372</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>▶ SKIN1004 (1 поз)</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Hyalu-Cica Sleeping Pack [30ml] / Увлажняющая гиалуроновая ночная маска для сухой кожи</t>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>214312149</v>
+        <v>437776835</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>294</v>
+        <v>820</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>3824</v>
+        <v>54102</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>3471</v>
+        <v>16236</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Итого SKIN1004</t>
+          <t xml:space="preserve">  Итого ROUND LAB</t>
         </is>
       </c>
       <c r="B51" s="9" t="n"/>
@@ -1755,41 +1755,108 @@
       <c r="D51" s="9" t="n"/>
       <c r="E51" s="9" t="n"/>
       <c r="F51" s="10" t="n">
-        <v>13</v>
+        <v>478</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>3824</v>
+        <v>504401</v>
       </c>
       <c r="H51" s="9" t="n"/>
       <c r="I51" s="10" t="n">
+        <v>151372</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>▶ SKIN1004 (1 поз)</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Hyalu-Cica Sleeping Pack [30ml] / Увлажняющая гиалуроновая ночная маска для сухой кожи</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>214312149</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>294</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>3824</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>267</v>
+      </c>
+      <c r="I53" s="7" t="n">
         <v>3471</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Итого SKIN1004</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="G54" s="10" t="n">
+        <v>3824</v>
+      </c>
+      <c r="H54" s="9" t="n"/>
+      <c r="I54" s="10" t="n">
+        <v>3471</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>ИТОГО ДОЗАКАЗ</t>
         </is>
       </c>
-      <c r="B53" s="12" t="n"/>
-      <c r="C53" s="12" t="n"/>
-      <c r="D53" s="12" t="n"/>
-      <c r="E53" s="12" t="n"/>
-      <c r="F53" s="13" t="n">
-        <v>9183</v>
-      </c>
-      <c r="G53" s="13" t="n">
-        <v>3332862</v>
-      </c>
-      <c r="H53" s="12" t="n"/>
-      <c r="I53" s="13" t="n">
-        <v>1948428</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="14" t="inlineStr">
-        <is>
-          <t>Дозаказать 9,183 шт на 3.33 млн ₽ закупа → потенциальная прибыль 1.95 млн ₽ за сезон. Товаров в списке: 27.</t>
+      <c r="B56" s="12" t="n"/>
+      <c r="C56" s="12" t="n"/>
+      <c r="D56" s="12" t="n"/>
+      <c r="E56" s="12" t="n"/>
+      <c r="F56" s="13" t="n">
+        <v>9380</v>
+      </c>
+      <c r="G56" s="13" t="n">
+        <v>3358642</v>
+      </c>
+      <c r="H56" s="12" t="n"/>
+      <c r="I56" s="13" t="n">
+        <v>1975811</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>Дозаказать 9,380 шт на 3.36 млн ₽ → прибыль 1.98 млн ₽. Позиций: 28.</t>
         </is>
       </c>
     </row>
